--- a/stage_matrix1.xlsx
+++ b/stage_matrix1.xlsx
@@ -1,21 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kevin\Documents\GitHub\NRES-470\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GIT\NRES-470\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32EEE2DB-B79D-4D43-8E38-1CB5504DE973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FAFCEF9F-E613-47FE-A8D8-92DD9509EF80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1060" yWindow="1060" windowWidth="16870" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-1620" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="stage_matrix1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -34,7 +39,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -97,7 +102,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C5700"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -490,27 +495,27 @@
     <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -589,7 +594,7 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
         <a:srgbClr val="ED7D31"/>
@@ -601,7 +606,7 @@
         <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
         <a:srgbClr val="70AD47"/>
@@ -648,6 +653,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -683,6 +705,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -834,11 +873,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -849,35 +888,35 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="C2">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="D2">
-        <v>0.82</v>
+        <v>0.9</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
       <c r="B3">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="C3">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -885,10 +924,10 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>0.65</v>
+        <v>0.35</v>
       </c>
       <c r="D4">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
     </row>
   </sheetData>
